--- a/results/supplement/Figure_2_data_meta_0p25_heterogeneity_0_pet_peese.xlsx
+++ b/results/supplement/Figure_2_data_meta_0p25_heterogeneity_0_pet_peese.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <si>
     <t xml:space="preserve">cID</t>
   </si>
@@ -1710,9 +1710,6 @@
   </si>
   <si>
     <t xml:space="preserve">439-2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">439-3</t>
   </si>
   <si>
     <t xml:space="preserve">439-4</t>
@@ -10362,18 +10359,22 @@
       <c r="A564" t="s">
         <v>566</v>
       </c>
-      <c r="B564"/>
-      <c r="C564" t="e">
-        <v>#NUM!</v>
-      </c>
-      <c r="D564"/>
+      <c r="B564" t="n">
+        <v>5.22992174761769</v>
+      </c>
+      <c r="C564" t="n">
+        <v>0</v>
+      </c>
+      <c r="D564" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="s">
         <v>567</v>
       </c>
       <c r="B565" t="n">
-        <v>5.22992174761769</v>
+        <v>5.2286533183728</v>
       </c>
       <c r="C565" t="n">
         <v>0</v>
@@ -10387,7 +10388,7 @@
         <v>568</v>
       </c>
       <c r="B566" t="n">
-        <v>5.2286533183728</v>
+        <v>5.01107224717052</v>
       </c>
       <c r="C566" t="n">
         <v>0</v>
@@ -10401,7 +10402,7 @@
         <v>569</v>
       </c>
       <c r="B567" t="n">
-        <v>5.01107224717052</v>
+        <v>5.00003345240809</v>
       </c>
       <c r="C567" t="n">
         <v>0</v>
@@ -10415,7 +10416,7 @@
         <v>570</v>
       </c>
       <c r="B568" t="n">
-        <v>5.00003345240809</v>
+        <v>5.00529886784011</v>
       </c>
       <c r="C568" t="n">
         <v>0</v>
@@ -10429,7 +10430,7 @@
         <v>571</v>
       </c>
       <c r="B569" t="n">
-        <v>5.00529886784011</v>
+        <v>5.7356638213643</v>
       </c>
       <c r="C569" t="n">
         <v>0</v>
@@ -10443,7 +10444,7 @@
         <v>572</v>
       </c>
       <c r="B570" t="n">
-        <v>5.7356638213643</v>
+        <v>8.65149432542565</v>
       </c>
       <c r="C570" t="n">
         <v>0</v>
@@ -10457,7 +10458,7 @@
         <v>573</v>
       </c>
       <c r="B571" t="n">
-        <v>8.65149432542565</v>
+        <v>6.11647862127969</v>
       </c>
       <c r="C571" t="n">
         <v>0</v>
@@ -10471,7 +10472,7 @@
         <v>574</v>
       </c>
       <c r="B572" t="n">
-        <v>6.11647862127969</v>
+        <v>5.05541437718425</v>
       </c>
       <c r="C572" t="n">
         <v>0</v>
@@ -10485,7 +10486,7 @@
         <v>575</v>
       </c>
       <c r="B573" t="n">
-        <v>5.05541437718425</v>
+        <v>5.3128410301962</v>
       </c>
       <c r="C573" t="n">
         <v>0</v>
@@ -10499,7 +10500,7 @@
         <v>576</v>
       </c>
       <c r="B574" t="n">
-        <v>5.3128410301962</v>
+        <v>5.13900839646608</v>
       </c>
       <c r="C574" t="n">
         <v>0</v>
@@ -10513,7 +10514,7 @@
         <v>577</v>
       </c>
       <c r="B575" t="n">
-        <v>5.13900839646608</v>
+        <v>6.88440914114233</v>
       </c>
       <c r="C575" t="n">
         <v>0</v>
@@ -10527,7 +10528,7 @@
         <v>578</v>
       </c>
       <c r="B576" t="n">
-        <v>6.88440914114233</v>
+        <v>9.50330233830725</v>
       </c>
       <c r="C576" t="n">
         <v>0</v>
@@ -10541,7 +10542,7 @@
         <v>579</v>
       </c>
       <c r="B577" t="n">
-        <v>9.50330233830725</v>
+        <v>5.62935203297237</v>
       </c>
       <c r="C577" t="n">
         <v>0</v>
@@ -10555,7 +10556,7 @@
         <v>580</v>
       </c>
       <c r="B578" t="n">
-        <v>5.62935203297237</v>
+        <v>8.65668725683254</v>
       </c>
       <c r="C578" t="n">
         <v>0</v>
@@ -10569,7 +10570,7 @@
         <v>581</v>
       </c>
       <c r="B579" t="n">
-        <v>8.65668725683254</v>
+        <v>6.70735385139558</v>
       </c>
       <c r="C579" t="n">
         <v>0</v>
@@ -10583,7 +10584,7 @@
         <v>582</v>
       </c>
       <c r="B580" t="n">
-        <v>6.70735385139558</v>
+        <v>5.06674586539439</v>
       </c>
       <c r="C580" t="n">
         <v>0</v>
@@ -10597,7 +10598,7 @@
         <v>583</v>
       </c>
       <c r="B581" t="n">
-        <v>5.06674586539439</v>
+        <v>5.28417045354207</v>
       </c>
       <c r="C581" t="n">
         <v>0</v>
@@ -10611,7 +10612,7 @@
         <v>584</v>
       </c>
       <c r="B582" t="n">
-        <v>5.28417045354207</v>
+        <v>5.00016828752597</v>
       </c>
       <c r="C582" t="n">
         <v>0</v>
@@ -10625,7 +10626,7 @@
         <v>585</v>
       </c>
       <c r="B583" t="n">
-        <v>5.00016828752597</v>
+        <v>5.07449309578771</v>
       </c>
       <c r="C583" t="n">
         <v>0</v>
@@ -10639,7 +10640,7 @@
         <v>586</v>
       </c>
       <c r="B584" t="n">
-        <v>5.07449309578771</v>
+        <v>5.00181528438445</v>
       </c>
       <c r="C584" t="n">
         <v>0</v>
@@ -10653,7 +10654,7 @@
         <v>587</v>
       </c>
       <c r="B585" t="n">
-        <v>5.00181528438445</v>
+        <v>5.02082494507158</v>
       </c>
       <c r="C585" t="n">
         <v>0</v>
@@ -10667,7 +10668,7 @@
         <v>588</v>
       </c>
       <c r="B586" t="n">
-        <v>5.02082494507158</v>
+        <v>5.26168459658128</v>
       </c>
       <c r="C586" t="n">
         <v>0</v>
@@ -10681,7 +10682,7 @@
         <v>589</v>
       </c>
       <c r="B587" t="n">
-        <v>5.26168459658128</v>
+        <v>5.19772368832326</v>
       </c>
       <c r="C587" t="n">
         <v>0</v>
@@ -10695,10 +10696,10 @@
         <v>590</v>
       </c>
       <c r="B588" t="n">
-        <v>5.19772368832326</v>
+        <v>5.92989287447361</v>
       </c>
       <c r="C588" t="n">
-        <v>0</v>
+        <v>0.302571860816944</v>
       </c>
       <c r="D588" t="b">
         <v>0</v>
@@ -10709,10 +10710,10 @@
         <v>591</v>
       </c>
       <c r="B589" t="n">
-        <v>5.92989287447361</v>
+        <v>7.12772421884067</v>
       </c>
       <c r="C589" t="n">
-        <v>0.302571860816944</v>
+        <v>0.987654320987654</v>
       </c>
       <c r="D589" t="b">
         <v>0</v>
@@ -10723,10 +10724,10 @@
         <v>592</v>
       </c>
       <c r="B590" t="n">
-        <v>7.12772421884067</v>
+        <v>5.01531899925308</v>
       </c>
       <c r="C590" t="n">
-        <v>0.987654320987654</v>
+        <v>0</v>
       </c>
       <c r="D590" t="b">
         <v>0</v>
@@ -10737,10 +10738,10 @@
         <v>593</v>
       </c>
       <c r="B591" t="n">
-        <v>5.01531899925308</v>
+        <v>12.114374908814</v>
       </c>
       <c r="C591" t="n">
-        <v>0</v>
+        <v>4.04040404040404</v>
       </c>
       <c r="D591" t="b">
         <v>0</v>
@@ -10751,10 +10752,10 @@
         <v>594</v>
       </c>
       <c r="B592" t="n">
-        <v>12.114374908814</v>
+        <v>57.1876235186465</v>
       </c>
       <c r="C592" t="n">
-        <v>4.04040404040404</v>
+        <v>4.25531914893617</v>
       </c>
       <c r="D592" t="b">
         <v>0</v>
@@ -10765,10 +10766,10 @@
         <v>595</v>
       </c>
       <c r="B593" t="n">
-        <v>57.1876235186465</v>
+        <v>5.03185767921326</v>
       </c>
       <c r="C593" t="n">
-        <v>4.25531914893617</v>
+        <v>0</v>
       </c>
       <c r="D593" t="b">
         <v>0</v>
@@ -10779,7 +10780,7 @@
         <v>596</v>
       </c>
       <c r="B594" t="n">
-        <v>5.03185767921326</v>
+        <v>5.05313969925155</v>
       </c>
       <c r="C594" t="n">
         <v>0</v>
@@ -10793,7 +10794,7 @@
         <v>597</v>
       </c>
       <c r="B595" t="n">
-        <v>5.05313969925155</v>
+        <v>5.18846070339971</v>
       </c>
       <c r="C595" t="n">
         <v>0</v>
@@ -10807,10 +10808,10 @@
         <v>598</v>
       </c>
       <c r="B596" t="n">
-        <v>5.18846070339971</v>
+        <v>8.11494183098004</v>
       </c>
       <c r="C596" t="n">
-        <v>0</v>
+        <v>2.13903743315508</v>
       </c>
       <c r="D596" t="b">
         <v>0</v>
@@ -10821,10 +10822,10 @@
         <v>599</v>
       </c>
       <c r="B597" t="n">
-        <v>8.11494183098004</v>
+        <v>8.03387371463793</v>
       </c>
       <c r="C597" t="n">
-        <v>2.13903743315508</v>
+        <v>16.1290322580645</v>
       </c>
       <c r="D597" t="b">
         <v>0</v>
@@ -10835,10 +10836,10 @@
         <v>600</v>
       </c>
       <c r="B598" t="n">
-        <v>8.03387371463793</v>
+        <v>5.14871332858951</v>
       </c>
       <c r="C598" t="n">
-        <v>16.1290322580645</v>
+        <v>0</v>
       </c>
       <c r="D598" t="b">
         <v>0</v>
@@ -10849,10 +10850,10 @@
         <v>601</v>
       </c>
       <c r="B599" t="n">
-        <v>5.14871332858951</v>
+        <v>6.82971055790871</v>
       </c>
       <c r="C599" t="n">
-        <v>0</v>
+        <v>1.03092783505155</v>
       </c>
       <c r="D599" t="b">
         <v>0</v>
@@ -10863,10 +10864,10 @@
         <v>602</v>
       </c>
       <c r="B600" t="n">
-        <v>6.82971055790871</v>
+        <v>64.8782024715854</v>
       </c>
       <c r="C600" t="n">
-        <v>1.03092783505155</v>
+        <v>45.5223880597015</v>
       </c>
       <c r="D600" t="b">
         <v>0</v>
@@ -10877,10 +10878,10 @@
         <v>603</v>
       </c>
       <c r="B601" t="n">
-        <v>64.8782024715854</v>
+        <v>9.02350563255633</v>
       </c>
       <c r="C601" t="n">
-        <v>45.5223880597015</v>
+        <v>13.5714285714286</v>
       </c>
       <c r="D601" t="b">
         <v>0</v>
@@ -10891,10 +10892,10 @@
         <v>604</v>
       </c>
       <c r="B602" t="n">
-        <v>9.02350563255633</v>
+        <v>8.61977499031187</v>
       </c>
       <c r="C602" t="n">
-        <v>13.5714285714286</v>
+        <v>6.32911392405063</v>
       </c>
       <c r="D602" t="b">
         <v>0</v>
@@ -10905,10 +10906,10 @@
         <v>605</v>
       </c>
       <c r="B603" t="n">
-        <v>8.61977499031187</v>
+        <v>5.03474308114704</v>
       </c>
       <c r="C603" t="n">
-        <v>6.32911392405063</v>
+        <v>0</v>
       </c>
       <c r="D603" t="b">
         <v>0</v>
@@ -10919,7 +10920,7 @@
         <v>606</v>
       </c>
       <c r="B604" t="n">
-        <v>5.03474308114704</v>
+        <v>5.3097626285369</v>
       </c>
       <c r="C604" t="n">
         <v>0</v>
@@ -10933,10 +10934,10 @@
         <v>607</v>
       </c>
       <c r="B605" t="n">
-        <v>5.3097626285369</v>
+        <v>11.4560234635306</v>
       </c>
       <c r="C605" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D605" t="b">
         <v>0</v>
@@ -10947,10 +10948,10 @@
         <v>608</v>
       </c>
       <c r="B606" t="n">
-        <v>11.4560234635306</v>
+        <v>6.32671370409362</v>
       </c>
       <c r="C606" t="n">
-        <v>12.5</v>
+        <v>5.40540540540541</v>
       </c>
       <c r="D606" t="b">
         <v>0</v>
@@ -10961,10 +10962,10 @@
         <v>609</v>
       </c>
       <c r="B607" t="n">
-        <v>6.32671370409362</v>
+        <v>6.22189507659768</v>
       </c>
       <c r="C607" t="n">
-        <v>5.40540540540541</v>
+        <v>0</v>
       </c>
       <c r="D607" t="b">
         <v>0</v>
@@ -10975,7 +10976,7 @@
         <v>610</v>
       </c>
       <c r="B608" t="n">
-        <v>6.22189507659768</v>
+        <v>6.24822999979501</v>
       </c>
       <c r="C608" t="n">
         <v>0</v>
@@ -10989,7 +10990,7 @@
         <v>611</v>
       </c>
       <c r="B609" t="n">
-        <v>6.24822999979501</v>
+        <v>6.09656697719876</v>
       </c>
       <c r="C609" t="n">
         <v>0</v>
@@ -11003,10 +11004,10 @@
         <v>612</v>
       </c>
       <c r="B610" t="n">
-        <v>6.09656697719876</v>
+        <v>32.146198092626</v>
       </c>
       <c r="C610" t="n">
-        <v>0</v>
+        <v>28.5714285714286</v>
       </c>
       <c r="D610" t="b">
         <v>0</v>
@@ -11017,10 +11018,10 @@
         <v>613</v>
       </c>
       <c r="B611" t="n">
-        <v>32.146198092626</v>
+        <v>23.9310906982224</v>
       </c>
       <c r="C611" t="n">
-        <v>28.5714285714286</v>
+        <v>17.6470588235294</v>
       </c>
       <c r="D611" t="b">
         <v>0</v>
@@ -11031,13 +11032,13 @@
         <v>614</v>
       </c>
       <c r="B612" t="n">
-        <v>23.9310906982224</v>
+        <v>99.9999999999963</v>
       </c>
       <c r="C612" t="n">
-        <v>17.6470588235294</v>
+        <v>54.5454545454545</v>
       </c>
       <c r="D612" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="613">
@@ -11045,13 +11046,13 @@
         <v>615</v>
       </c>
       <c r="B613" t="n">
-        <v>99.9999999999963</v>
+        <v>5.42792963449549</v>
       </c>
       <c r="C613" t="n">
-        <v>54.5454545454545</v>
+        <v>0</v>
       </c>
       <c r="D613" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
@@ -11059,7 +11060,7 @@
         <v>616</v>
       </c>
       <c r="B614" t="n">
-        <v>5.42792963449549</v>
+        <v>6.23100167940237</v>
       </c>
       <c r="C614" t="n">
         <v>0</v>
@@ -11073,7 +11074,7 @@
         <v>617</v>
       </c>
       <c r="B615" t="n">
-        <v>6.23100167940237</v>
+        <v>5.20375050410668</v>
       </c>
       <c r="C615" t="n">
         <v>0</v>
@@ -11087,10 +11088,10 @@
         <v>618</v>
       </c>
       <c r="B616" t="n">
-        <v>5.20375050410668</v>
+        <v>13.8586465743367</v>
       </c>
       <c r="C616" t="n">
-        <v>0</v>
+        <v>16.6666666666667</v>
       </c>
       <c r="D616" t="b">
         <v>0</v>
@@ -11101,10 +11102,10 @@
         <v>619</v>
       </c>
       <c r="B617" t="n">
-        <v>13.8586465743367</v>
+        <v>6.89275562678226</v>
       </c>
       <c r="C617" t="n">
-        <v>16.6666666666667</v>
+        <v>6.61157024793388</v>
       </c>
       <c r="D617" t="b">
         <v>0</v>
@@ -11115,10 +11116,10 @@
         <v>620</v>
       </c>
       <c r="B618" t="n">
-        <v>6.89275562678226</v>
+        <v>5.03119420824597</v>
       </c>
       <c r="C618" t="n">
-        <v>6.61157024793388</v>
+        <v>0</v>
       </c>
       <c r="D618" t="b">
         <v>0</v>
@@ -11129,10 +11130,10 @@
         <v>621</v>
       </c>
       <c r="B619" t="n">
-        <v>5.03119420824597</v>
+        <v>5.85934369282221</v>
       </c>
       <c r="C619" t="n">
-        <v>0</v>
+        <v>0.555555555555556</v>
       </c>
       <c r="D619" t="b">
         <v>0</v>
@@ -11143,10 +11144,10 @@
         <v>622</v>
       </c>
       <c r="B620" t="n">
-        <v>5.85934369282221</v>
+        <v>5.03658156511116</v>
       </c>
       <c r="C620" t="n">
-        <v>0.555555555555556</v>
+        <v>0</v>
       </c>
       <c r="D620" t="b">
         <v>0</v>
@@ -11157,10 +11158,10 @@
         <v>623</v>
       </c>
       <c r="B621" t="n">
-        <v>5.03658156511116</v>
+        <v>7.04723841542362</v>
       </c>
       <c r="C621" t="n">
-        <v>0</v>
+        <v>2.73972602739726</v>
       </c>
       <c r="D621" t="b">
         <v>0</v>
@@ -11171,10 +11172,10 @@
         <v>624</v>
       </c>
       <c r="B622" t="n">
-        <v>7.04723841542362</v>
+        <v>5.41481413276136</v>
       </c>
       <c r="C622" t="n">
-        <v>2.73972602739726</v>
+        <v>0</v>
       </c>
       <c r="D622" t="b">
         <v>0</v>
@@ -11185,7 +11186,7 @@
         <v>625</v>
       </c>
       <c r="B623" t="n">
-        <v>5.41481413276136</v>
+        <v>5.59715291401123</v>
       </c>
       <c r="C623" t="n">
         <v>0</v>
@@ -11199,7 +11200,7 @@
         <v>626</v>
       </c>
       <c r="B624" t="n">
-        <v>5.59715291401123</v>
+        <v>5.09658218731418</v>
       </c>
       <c r="C624" t="n">
         <v>0</v>
@@ -11213,7 +11214,7 @@
         <v>627</v>
       </c>
       <c r="B625" t="n">
-        <v>5.09658218731418</v>
+        <v>5.52769681615503</v>
       </c>
       <c r="C625" t="n">
         <v>0</v>
@@ -11227,7 +11228,7 @@
         <v>628</v>
       </c>
       <c r="B626" t="n">
-        <v>5.52769681615503</v>
+        <v>5.53516232052586</v>
       </c>
       <c r="C626" t="n">
         <v>0</v>
@@ -11241,7 +11242,7 @@
         <v>629</v>
       </c>
       <c r="B627" t="n">
-        <v>5.53516232052586</v>
+        <v>5.39817544081159</v>
       </c>
       <c r="C627" t="n">
         <v>0</v>
@@ -11255,7 +11256,7 @@
         <v>630</v>
       </c>
       <c r="B628" t="n">
-        <v>5.39817544081159</v>
+        <v>5.08969395448472</v>
       </c>
       <c r="C628" t="n">
         <v>0</v>
@@ -11269,7 +11270,7 @@
         <v>631</v>
       </c>
       <c r="B629" t="n">
-        <v>5.08969395448472</v>
+        <v>5.35257628255614</v>
       </c>
       <c r="C629" t="n">
         <v>0</v>
@@ -11283,7 +11284,7 @@
         <v>632</v>
       </c>
       <c r="B630" t="n">
-        <v>5.35257628255614</v>
+        <v>5.01766159918525</v>
       </c>
       <c r="C630" t="n">
         <v>0</v>
@@ -11297,7 +11298,7 @@
         <v>633</v>
       </c>
       <c r="B631" t="n">
-        <v>5.01766159918525</v>
+        <v>5.42968860382236</v>
       </c>
       <c r="C631" t="n">
         <v>0</v>
@@ -11311,7 +11312,7 @@
         <v>634</v>
       </c>
       <c r="B632" t="n">
-        <v>5.42968860382236</v>
+        <v>5.63764012847899</v>
       </c>
       <c r="C632" t="n">
         <v>0</v>
@@ -11325,7 +11326,7 @@
         <v>635</v>
       </c>
       <c r="B633" t="n">
-        <v>5.63764012847899</v>
+        <v>5.28502126580379</v>
       </c>
       <c r="C633" t="n">
         <v>0</v>
@@ -11339,7 +11340,7 @@
         <v>636</v>
       </c>
       <c r="B634" t="n">
-        <v>5.28502126580379</v>
+        <v>5.69773380028176</v>
       </c>
       <c r="C634" t="n">
         <v>0</v>
@@ -11353,7 +11354,7 @@
         <v>637</v>
       </c>
       <c r="B635" t="n">
-        <v>5.69773380028176</v>
+        <v>5.00002702853112</v>
       </c>
       <c r="C635" t="n">
         <v>0</v>
@@ -11367,7 +11368,7 @@
         <v>638</v>
       </c>
       <c r="B636" t="n">
-        <v>5.00002702853112</v>
+        <v>8.23203403226071</v>
       </c>
       <c r="C636" t="n">
         <v>0</v>
@@ -11381,7 +11382,7 @@
         <v>639</v>
       </c>
       <c r="B637" t="n">
-        <v>8.23203403226071</v>
+        <v>5.52025039821992</v>
       </c>
       <c r="C637" t="n">
         <v>0</v>
@@ -11395,7 +11396,7 @@
         <v>640</v>
       </c>
       <c r="B638" t="n">
-        <v>5.52025039821992</v>
+        <v>7.63997056178605</v>
       </c>
       <c r="C638" t="n">
         <v>0</v>
@@ -11409,7 +11410,7 @@
         <v>641</v>
       </c>
       <c r="B639" t="n">
-        <v>7.63997056178605</v>
+        <v>5.11630210291621</v>
       </c>
       <c r="C639" t="n">
         <v>0</v>
@@ -11423,7 +11424,7 @@
         <v>642</v>
       </c>
       <c r="B640" t="n">
-        <v>5.11630210291621</v>
+        <v>5.21750465383623</v>
       </c>
       <c r="C640" t="n">
         <v>0</v>
@@ -11437,7 +11438,7 @@
         <v>643</v>
       </c>
       <c r="B641" t="n">
-        <v>5.21750465383623</v>
+        <v>5.87567689865834</v>
       </c>
       <c r="C641" t="n">
         <v>0</v>
@@ -11451,7 +11452,7 @@
         <v>644</v>
       </c>
       <c r="B642" t="n">
-        <v>5.87567689865834</v>
+        <v>7.45280846023219</v>
       </c>
       <c r="C642" t="n">
         <v>0</v>
@@ -11465,7 +11466,7 @@
         <v>645</v>
       </c>
       <c r="B643" t="n">
-        <v>7.45280846023219</v>
+        <v>5.17636085066878</v>
       </c>
       <c r="C643" t="n">
         <v>0</v>
@@ -11479,7 +11480,7 @@
         <v>646</v>
       </c>
       <c r="B644" t="n">
-        <v>5.17636085066878</v>
+        <v>6.10178454135785</v>
       </c>
       <c r="C644" t="n">
         <v>0</v>
@@ -11493,7 +11494,7 @@
         <v>647</v>
       </c>
       <c r="B645" t="n">
-        <v>6.10178454135785</v>
+        <v>6.06131315597566</v>
       </c>
       <c r="C645" t="n">
         <v>0</v>
@@ -11507,7 +11508,7 @@
         <v>648</v>
       </c>
       <c r="B646" t="n">
-        <v>6.06131315597566</v>
+        <v>5.68868121607993</v>
       </c>
       <c r="C646" t="n">
         <v>0</v>
@@ -11521,7 +11522,7 @@
         <v>649</v>
       </c>
       <c r="B647" t="n">
-        <v>5.68868121607993</v>
+        <v>5.92449407564614</v>
       </c>
       <c r="C647" t="n">
         <v>0</v>
@@ -11535,7 +11536,7 @@
         <v>650</v>
       </c>
       <c r="B648" t="n">
-        <v>5.92449407564614</v>
+        <v>5.32439900846185</v>
       </c>
       <c r="C648" t="n">
         <v>0</v>
@@ -11549,7 +11550,7 @@
         <v>651</v>
       </c>
       <c r="B649" t="n">
-        <v>5.32439900846185</v>
+        <v>5.15018489527881</v>
       </c>
       <c r="C649" t="n">
         <v>0</v>
@@ -11563,7 +11564,7 @@
         <v>652</v>
       </c>
       <c r="B650" t="n">
-        <v>5.15018489527881</v>
+        <v>5.62382346788196</v>
       </c>
       <c r="C650" t="n">
         <v>0</v>
@@ -11577,7 +11578,7 @@
         <v>653</v>
       </c>
       <c r="B651" t="n">
-        <v>5.62382346788196</v>
+        <v>6.84786553815663</v>
       </c>
       <c r="C651" t="n">
         <v>0</v>
@@ -11591,7 +11592,7 @@
         <v>654</v>
       </c>
       <c r="B652" t="n">
-        <v>6.84786553815663</v>
+        <v>12.2558530135046</v>
       </c>
       <c r="C652" t="n">
         <v>0</v>
@@ -11605,7 +11606,7 @@
         <v>655</v>
       </c>
       <c r="B653" t="n">
-        <v>12.2558530135046</v>
+        <v>8.28118014047018</v>
       </c>
       <c r="C653" t="n">
         <v>0</v>
@@ -11619,7 +11620,7 @@
         <v>656</v>
       </c>
       <c r="B654" t="n">
-        <v>8.28118014047018</v>
+        <v>5.02883283289919</v>
       </c>
       <c r="C654" t="n">
         <v>0</v>
@@ -11633,7 +11634,7 @@
         <v>657</v>
       </c>
       <c r="B655" t="n">
-        <v>5.02883283289919</v>
+        <v>5.33584737829077</v>
       </c>
       <c r="C655" t="n">
         <v>0</v>
@@ -11647,7 +11648,7 @@
         <v>658</v>
       </c>
       <c r="B656" t="n">
-        <v>5.33584737829077</v>
+        <v>5.19629820558511</v>
       </c>
       <c r="C656" t="n">
         <v>0</v>
@@ -11661,7 +11662,7 @@
         <v>659</v>
       </c>
       <c r="B657" t="n">
-        <v>5.19629820558511</v>
+        <v>5.10167725040024</v>
       </c>
       <c r="C657" t="n">
         <v>0</v>
@@ -11675,7 +11676,7 @@
         <v>660</v>
       </c>
       <c r="B658" t="n">
-        <v>5.10167725040024</v>
+        <v>5.18902080201361</v>
       </c>
       <c r="C658" t="n">
         <v>0</v>
@@ -11689,7 +11690,7 @@
         <v>661</v>
       </c>
       <c r="B659" t="n">
-        <v>5.18902080201361</v>
+        <v>8.06049797518489</v>
       </c>
       <c r="C659" t="n">
         <v>0</v>
@@ -11703,7 +11704,7 @@
         <v>662</v>
       </c>
       <c r="B660" t="n">
-        <v>8.06049797518489</v>
+        <v>5.6330759788897</v>
       </c>
       <c r="C660" t="n">
         <v>0</v>
@@ -11717,7 +11718,7 @@
         <v>663</v>
       </c>
       <c r="B661" t="n">
-        <v>5.6330759788897</v>
+        <v>6.08275230817745</v>
       </c>
       <c r="C661" t="n">
         <v>0</v>
@@ -11731,7 +11732,7 @@
         <v>664</v>
       </c>
       <c r="B662" t="n">
-        <v>6.08275230817745</v>
+        <v>5.00326649576064</v>
       </c>
       <c r="C662" t="n">
         <v>0</v>
@@ -11745,7 +11746,7 @@
         <v>665</v>
       </c>
       <c r="B663" t="n">
-        <v>5.00326649576064</v>
+        <v>13.3515685974933</v>
       </c>
       <c r="C663" t="n">
         <v>0</v>
@@ -11759,10 +11760,10 @@
         <v>666</v>
       </c>
       <c r="B664" t="n">
-        <v>13.3515685974933</v>
+        <v>38.4114466603136</v>
       </c>
       <c r="C664" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="D664" t="b">
         <v>0</v>
@@ -11773,10 +11774,10 @@
         <v>667</v>
       </c>
       <c r="B665" t="n">
-        <v>38.4114466603136</v>
+        <v>7.87102493105438</v>
       </c>
       <c r="C665" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="D665" t="b">
         <v>0</v>
@@ -11787,7 +11788,7 @@
         <v>668</v>
       </c>
       <c r="B666" t="n">
-        <v>7.87102493105438</v>
+        <v>5.00071368982664</v>
       </c>
       <c r="C666" t="n">
         <v>0</v>
@@ -11801,7 +11802,7 @@
         <v>669</v>
       </c>
       <c r="B667" t="n">
-        <v>5.00071368982664</v>
+        <v>5.72216058902983</v>
       </c>
       <c r="C667" t="n">
         <v>0</v>
@@ -11815,7 +11816,7 @@
         <v>670</v>
       </c>
       <c r="B668" t="n">
-        <v>5.72216058902983</v>
+        <v>11.2456862233724</v>
       </c>
       <c r="C668" t="n">
         <v>0</v>
@@ -11829,7 +11830,7 @@
         <v>671</v>
       </c>
       <c r="B669" t="n">
-        <v>11.2456862233724</v>
+        <v>5.00514100343107</v>
       </c>
       <c r="C669" t="n">
         <v>0</v>
@@ -11843,7 +11844,7 @@
         <v>672</v>
       </c>
       <c r="B670" t="n">
-        <v>5.00514100343107</v>
+        <v>13.7503805617554</v>
       </c>
       <c r="C670" t="n">
         <v>0</v>
@@ -11857,7 +11858,7 @@
         <v>673</v>
       </c>
       <c r="B671" t="n">
-        <v>13.7503805617554</v>
+        <v>5.04968263326432</v>
       </c>
       <c r="C671" t="n">
         <v>0</v>
@@ -11871,7 +11872,7 @@
         <v>674</v>
       </c>
       <c r="B672" t="n">
-        <v>5.04968263326432</v>
+        <v>5.15273519614271</v>
       </c>
       <c r="C672" t="n">
         <v>0</v>
@@ -11885,7 +11886,7 @@
         <v>675</v>
       </c>
       <c r="B673" t="n">
-        <v>5.15273519614271</v>
+        <v>6.19058220039127</v>
       </c>
       <c r="C673" t="n">
         <v>0</v>
@@ -11899,7 +11900,7 @@
         <v>676</v>
       </c>
       <c r="B674" t="n">
-        <v>6.19058220039127</v>
+        <v>5.00001605117539</v>
       </c>
       <c r="C674" t="n">
         <v>0</v>
@@ -11913,7 +11914,7 @@
         <v>677</v>
       </c>
       <c r="B675" t="n">
-        <v>5.00001605117539</v>
+        <v>6.70061113355102</v>
       </c>
       <c r="C675" t="n">
         <v>0</v>
@@ -11927,7 +11928,7 @@
         <v>678</v>
       </c>
       <c r="B676" t="n">
-        <v>6.70061113355102</v>
+        <v>5.00099870452234</v>
       </c>
       <c r="C676" t="n">
         <v>0</v>
@@ -11941,7 +11942,7 @@
         <v>679</v>
       </c>
       <c r="B677" t="n">
-        <v>5.00099870452234</v>
+        <v>5.11701183959265</v>
       </c>
       <c r="C677" t="n">
         <v>0</v>
@@ -11955,7 +11956,7 @@
         <v>680</v>
       </c>
       <c r="B678" t="n">
-        <v>5.11701183959265</v>
+        <v>5.00153023918106</v>
       </c>
       <c r="C678" t="n">
         <v>0</v>
@@ -11969,7 +11970,7 @@
         <v>681</v>
       </c>
       <c r="B679" t="n">
-        <v>5.00153023918106</v>
+        <v>8.73965358374162</v>
       </c>
       <c r="C679" t="n">
         <v>0</v>
@@ -11983,13 +11984,13 @@
         <v>682</v>
       </c>
       <c r="B680" t="n">
-        <v>8.73965358374162</v>
+        <v>100</v>
       </c>
       <c r="C680" t="n">
-        <v>0</v>
+        <v>73.4615384615385</v>
       </c>
       <c r="D680" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681">
@@ -11997,10 +11998,10 @@
         <v>683</v>
       </c>
       <c r="B681" t="n">
-        <v>100</v>
+        <v>88.8399159680283</v>
       </c>
       <c r="C681" t="n">
-        <v>73.4615384615385</v>
+        <v>51.077943615257</v>
       </c>
       <c r="D681" t="b">
         <v>1</v>
@@ -12011,10 +12012,10 @@
         <v>684</v>
       </c>
       <c r="B682" t="n">
-        <v>88.8399159680283</v>
+        <v>100</v>
       </c>
       <c r="C682" t="n">
-        <v>51.077943615257</v>
+        <v>97.0588235294118</v>
       </c>
       <c r="D682" t="b">
         <v>1</v>
@@ -12028,7 +12029,7 @@
         <v>100</v>
       </c>
       <c r="C683" t="n">
-        <v>97.0588235294118</v>
+        <v>58.0645161290323</v>
       </c>
       <c r="D683" t="b">
         <v>1</v>
@@ -12039,10 +12040,10 @@
         <v>686</v>
       </c>
       <c r="B684" t="n">
-        <v>100</v>
+        <v>99.9999999957085</v>
       </c>
       <c r="C684" t="n">
-        <v>58.0645161290323</v>
+        <v>67.5824175824176</v>
       </c>
       <c r="D684" t="b">
         <v>1</v>
@@ -12053,10 +12054,10 @@
         <v>687</v>
       </c>
       <c r="B685" t="n">
-        <v>99.9999999957085</v>
+        <v>99.9999733353755</v>
       </c>
       <c r="C685" t="n">
-        <v>67.5824175824176</v>
+        <v>71.7557251908397</v>
       </c>
       <c r="D685" t="b">
         <v>1</v>
@@ -12067,10 +12068,10 @@
         <v>688</v>
       </c>
       <c r="B686" t="n">
-        <v>99.9999733353755</v>
+        <v>100</v>
       </c>
       <c r="C686" t="n">
-        <v>71.7557251908397</v>
+        <v>83.3333333333333</v>
       </c>
       <c r="D686" t="b">
         <v>1</v>
@@ -12081,10 +12082,10 @@
         <v>689</v>
       </c>
       <c r="B687" t="n">
-        <v>100</v>
+        <v>93.3191106636875</v>
       </c>
       <c r="C687" t="n">
-        <v>83.3333333333333</v>
+        <v>55.5555555555556</v>
       </c>
       <c r="D687" t="b">
         <v>1</v>
@@ -12095,10 +12096,10 @@
         <v>690</v>
       </c>
       <c r="B688" t="n">
-        <v>93.3191106636875</v>
+        <v>100</v>
       </c>
       <c r="C688" t="n">
-        <v>55.5555555555556</v>
+        <v>80.791788856305</v>
       </c>
       <c r="D688" t="b">
         <v>1</v>
@@ -12109,10 +12110,10 @@
         <v>691</v>
       </c>
       <c r="B689" t="n">
-        <v>100</v>
+        <v>96.9429828932395</v>
       </c>
       <c r="C689" t="n">
-        <v>80.791788856305</v>
+        <v>68.75</v>
       </c>
       <c r="D689" t="b">
         <v>1</v>
@@ -12123,10 +12124,10 @@
         <v>692</v>
       </c>
       <c r="B690" t="n">
-        <v>96.9429828932395</v>
+        <v>93.5002182893151</v>
       </c>
       <c r="C690" t="n">
-        <v>68.75</v>
+        <v>51.1627906976744</v>
       </c>
       <c r="D690" t="b">
         <v>1</v>
@@ -12137,10 +12138,10 @@
         <v>693</v>
       </c>
       <c r="B691" t="n">
-        <v>93.5002182893151</v>
+        <v>100</v>
       </c>
       <c r="C691" t="n">
-        <v>51.1627906976744</v>
+        <v>99.3506493506494</v>
       </c>
       <c r="D691" t="b">
         <v>1</v>
@@ -12151,13 +12152,13 @@
         <v>694</v>
       </c>
       <c r="B692" t="n">
-        <v>100</v>
+        <v>10.4065133446721</v>
       </c>
       <c r="C692" t="n">
-        <v>99.3506493506494</v>
+        <v>0</v>
       </c>
       <c r="D692" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
@@ -12165,10 +12166,10 @@
         <v>695</v>
       </c>
       <c r="B693" t="n">
-        <v>10.4065133446721</v>
+        <v>23.0314184577067</v>
       </c>
       <c r="C693" t="n">
-        <v>0</v>
+        <v>7.92079207920792</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -12179,10 +12180,10 @@
         <v>696</v>
       </c>
       <c r="B694" t="n">
-        <v>23.0314184577067</v>
+        <v>5.00713172709876</v>
       </c>
       <c r="C694" t="n">
-        <v>7.92079207920792</v>
+        <v>0</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -12193,10 +12194,10 @@
         <v>697</v>
       </c>
       <c r="B695" t="n">
-        <v>5.00713172709876</v>
+        <v>5.03565947948979</v>
       </c>
       <c r="C695" t="n">
-        <v>0</v>
+        <v>2.04081632653061</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -12207,10 +12208,10 @@
         <v>698</v>
       </c>
       <c r="B696" t="n">
-        <v>5.03565947948979</v>
+        <v>5.35225272094203</v>
       </c>
       <c r="C696" t="n">
-        <v>2.04081632653061</v>
+        <v>0</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -12221,7 +12222,7 @@
         <v>699</v>
       </c>
       <c r="B697" t="n">
-        <v>5.35225272094203</v>
+        <v>5.23022495166284</v>
       </c>
       <c r="C697" t="n">
         <v>0</v>
@@ -12235,7 +12236,7 @@
         <v>700</v>
       </c>
       <c r="B698" t="n">
-        <v>5.23022495166284</v>
+        <v>5.01423283500585</v>
       </c>
       <c r="C698" t="n">
         <v>0</v>
@@ -12249,10 +12250,10 @@
         <v>701</v>
       </c>
       <c r="B699" t="n">
-        <v>5.01423283500585</v>
+        <v>7.64509114539819</v>
       </c>
       <c r="C699" t="n">
-        <v>0</v>
+        <v>7.69230769230769</v>
       </c>
       <c r="D699" t="b">
         <v>0</v>
@@ -12263,10 +12264,10 @@
         <v>702</v>
       </c>
       <c r="B700" t="n">
-        <v>7.64509114539819</v>
+        <v>6.07319644423374</v>
       </c>
       <c r="C700" t="n">
-        <v>7.69230769230769</v>
+        <v>0</v>
       </c>
       <c r="D700" t="b">
         <v>0</v>
@@ -12277,7 +12278,7 @@
         <v>703</v>
       </c>
       <c r="B701" t="n">
-        <v>6.07319644423374</v>
+        <v>6.878906329815</v>
       </c>
       <c r="C701" t="n">
         <v>0</v>
@@ -12291,7 +12292,7 @@
         <v>704</v>
       </c>
       <c r="B702" t="n">
-        <v>6.878906329815</v>
+        <v>5.02277251458878</v>
       </c>
       <c r="C702" t="n">
         <v>0</v>
@@ -12305,7 +12306,7 @@
         <v>705</v>
       </c>
       <c r="B703" t="n">
-        <v>5.02277251458878</v>
+        <v>10.3372440188289</v>
       </c>
       <c r="C703" t="n">
         <v>0</v>
@@ -12319,7 +12320,7 @@
         <v>706</v>
       </c>
       <c r="B704" t="n">
-        <v>10.3372440188289</v>
+        <v>7.24475641259443</v>
       </c>
       <c r="C704" t="n">
         <v>0</v>
@@ -12333,7 +12334,7 @@
         <v>707</v>
       </c>
       <c r="B705" t="n">
-        <v>7.24475641259443</v>
+        <v>5.53445961393135</v>
       </c>
       <c r="C705" t="n">
         <v>0</v>
@@ -12347,7 +12348,7 @@
         <v>708</v>
       </c>
       <c r="B706" t="n">
-        <v>5.53445961393135</v>
+        <v>7.51118828575155</v>
       </c>
       <c r="C706" t="n">
         <v>0</v>
@@ -12361,7 +12362,7 @@
         <v>709</v>
       </c>
       <c r="B707" t="n">
-        <v>7.51118828575155</v>
+        <v>5.05889544380971</v>
       </c>
       <c r="C707" t="n">
         <v>0</v>
@@ -12375,26 +12376,12 @@
         <v>710</v>
       </c>
       <c r="B708" t="n">
-        <v>5.05889544380971</v>
+        <v>5.04629749373369</v>
       </c>
       <c r="C708" t="n">
         <v>0</v>
       </c>
       <c r="D708" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="709">
-      <c r="A709" t="s">
-        <v>711</v>
-      </c>
-      <c r="B709" t="n">
-        <v>5.04629749373369</v>
-      </c>
-      <c r="C709" t="n">
-        <v>0</v>
-      </c>
-      <c r="D709" t="b">
         <v>0</v>
       </c>
     </row>
